--- a/Files/Files/Building/BOM.xlsx
+++ b/Files/Files/Building/BOM.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
+  <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="164011"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648"/>
   </bookViews>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="31">
   <si>
     <t>Smart Car 2WD</t>
   </si>
@@ -87,19 +87,31 @@
     <t>9V Li-ion Battery</t>
   </si>
   <si>
-    <t>https://www.wildberries.am/catalog/306803553/detail.aspx</t>
-  </si>
-  <si>
-    <t>https://www.list.am/item/21538828?ld_src=2</t>
-  </si>
-  <si>
-    <t>from list.am</t>
-  </si>
-  <si>
-    <t>https://www.list.am/item/21487709?ld_src=2</t>
-  </si>
-  <si>
     <t>from temu</t>
+  </si>
+  <si>
+    <t>Esp32 Cam</t>
+  </si>
+  <si>
+    <t>for capturing the surroundings and collecting data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SG90 </t>
+  </si>
+  <si>
+    <t>to rotate the camera</t>
+  </si>
+  <si>
+    <t>Open in WB</t>
+  </si>
+  <si>
+    <t>Open in List.am</t>
+  </si>
+  <si>
+    <t>Open in Temu</t>
+  </si>
+  <si>
+    <t>Ordered</t>
   </si>
 </sst>
 </file>
@@ -453,16 +465,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:H19"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.6640625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="12.21875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="14.109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="42" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
@@ -512,8 +526,8 @@
       <c r="F2" t="s">
         <v>12</v>
       </c>
-      <c r="G2" t="s">
-        <v>24</v>
+      <c r="G2" s="5" t="s">
+        <v>28</v>
       </c>
       <c r="H2" t="s">
         <v>14</v>
@@ -527,21 +541,21 @@
         <v>3</v>
       </c>
       <c r="C3" s="1">
-        <f t="shared" ref="C3:C7" si="0">D3*0.0028</f>
+        <f t="shared" ref="C3:C9" si="0">D3*0.0028</f>
         <v>1.4</v>
       </c>
       <c r="D3" s="2">
         <v>500</v>
       </c>
       <c r="E3" s="4">
-        <f t="shared" ref="E3:E19" si="1">B3*C3</f>
+        <f t="shared" ref="E3:E9" si="1">B3*C3</f>
         <v>4.1999999999999993</v>
       </c>
       <c r="F3" t="s">
         <v>13</v>
       </c>
-      <c r="G3" t="s">
-        <v>25</v>
+      <c r="G3" s="5" t="s">
+        <v>28</v>
       </c>
       <c r="H3" t="s">
         <v>15</v>
@@ -569,7 +583,7 @@
         <v>12</v>
       </c>
       <c r="G4" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="H4" t="s">
         <v>16</v>
@@ -597,7 +611,7 @@
         <v>12</v>
       </c>
       <c r="G5" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="H5" t="s">
         <v>19</v>
@@ -625,7 +639,7 @@
         <v>13</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="H6" t="s">
         <v>20</v>
@@ -653,21 +667,67 @@
         <v>13</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="H7" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="C8" s="1"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="4"/>
+      <c r="A8" t="s">
+        <v>23</v>
+      </c>
+      <c r="B8">
+        <v>1</v>
+      </c>
+      <c r="C8" s="1">
+        <f t="shared" si="0"/>
+        <v>12.6</v>
+      </c>
+      <c r="D8" s="2">
+        <v>4500</v>
+      </c>
+      <c r="E8" s="4">
+        <f t="shared" si="1"/>
+        <v>12.6</v>
+      </c>
+      <c r="F8" t="s">
+        <v>30</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="H8" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="C9" s="1"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="4"/>
+      <c r="A9" t="s">
+        <v>25</v>
+      </c>
+      <c r="B9">
+        <v>2</v>
+      </c>
+      <c r="C9" s="1">
+        <f t="shared" si="0"/>
+        <v>1.4</v>
+      </c>
+      <c r="D9" s="2">
+        <v>500</v>
+      </c>
+      <c r="E9" s="4">
+        <f t="shared" si="1"/>
+        <v>2.8</v>
+      </c>
+      <c r="F9" t="s">
+        <v>12</v>
+      </c>
+      <c r="G9" t="s">
+        <v>22</v>
+      </c>
+      <c r="H9" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C10" s="1"/>
@@ -721,10 +781,13 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="G6" r:id="rId1"/>
-    <hyperlink ref="G7" r:id="rId2"/>
+    <hyperlink ref="G8" r:id="rId1"/>
+    <hyperlink ref="G6" r:id="rId2"/>
+    <hyperlink ref="G3" r:id="rId3" display="https://www.list.am/item/21487709?ld_src=2"/>
+    <hyperlink ref="G7" r:id="rId4"/>
+    <hyperlink ref="G2" r:id="rId5"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="0" orientation="portrait" horizontalDpi="203" verticalDpi="203" r:id="rId3"/>
+  <pageSetup paperSize="0" orientation="portrait" horizontalDpi="203" verticalDpi="203" r:id="rId6"/>
 </worksheet>
 </file>
--- a/Files/Files/Building/BOM.xlsx
+++ b/Files/Files/Building/BOM.xlsx
@@ -542,20 +542,20 @@
       </c>
       <c r="C3" s="1">
         <f t="shared" ref="C3:C9" si="0">D3*0.0028</f>
-        <v>1.4</v>
+        <v>0.55999999999999994</v>
       </c>
       <c r="D3" s="2">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="E3" s="4">
         <f t="shared" ref="E3:E9" si="1">B3*C3</f>
-        <v>4.1999999999999993</v>
+        <v>1.6799999999999997</v>
       </c>
       <c r="F3" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H3" t="s">
         <v>15</v>
@@ -783,7 +783,7 @@
   <hyperlinks>
     <hyperlink ref="G8" r:id="rId1"/>
     <hyperlink ref="G6" r:id="rId2"/>
-    <hyperlink ref="G3" r:id="rId3" display="https://www.list.am/item/21487709?ld_src=2"/>
+    <hyperlink ref="G3" r:id="rId3"/>
     <hyperlink ref="G7" r:id="rId4"/>
     <hyperlink ref="G2" r:id="rId5"/>
   </hyperlinks>
